--- a/relatorio_dolar.xlsx
+++ b/relatorio_dolar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R$ 5.1218</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R$ 5.1231</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 5.0704</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>R$ 5.1188</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,27 +995,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R$ 5.1385</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R$ 5.1390</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 5.0950</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>R$ 5.1378</t>
+          <t>R$ 5.0842</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1027,27 +1027,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R$ 5.1437</t>
+          <t>R$ 5.1218</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R$ 5.1443</t>
+          <t>R$ 5.1231</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 5.1022</t>
+          <t>R$ 5.0704</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>R$ 5.1436</t>
+          <t>R$ 5.1188</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1059,27 +1059,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R$ 5.1029</t>
+          <t>R$ 5.1218</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R$ 5.1513</t>
+          <t>R$ 5.1231</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 5.0746</t>
+          <t>R$ 5.0704</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>R$ 5.1030</t>
+          <t>R$ 5.1188</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R$ 5.0727</t>
+          <t>R$ 5.1218</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R$ 5.1185</t>
+          <t>R$ 5.1231</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 5.0558</t>
+          <t>R$ 5.0704</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>R$ 5.0727</t>
+          <t>R$ 5.1188</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1123,27 +1123,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R$ 5.0781</t>
+          <t>R$ 5.1385</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R$ 5.1272</t>
+          <t>R$ 5.1390</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 5.0533</t>
+          <t>R$ 5.0950</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>R$ 5.0771</t>
+          <t>R$ 5.1378</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1155,27 +1155,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R$ 5.1271</t>
+          <t>R$ 5.1385</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>R$ 5.1285</t>
+          <t>R$ 5.1390</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 5.0702</t>
+          <t>R$ 5.0950</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>R$ 5.1275</t>
+          <t>R$ 5.1378</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1187,27 +1187,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R$ 5.1371</t>
+          <t>R$ 5.1385</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>R$ 5.1699</t>
+          <t>R$ 5.1390</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 5.1033</t>
+          <t>R$ 5.0950</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>R$ 5.1313</t>
+          <t>R$ 5.1378</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1219,27 +1219,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R$ 5.1230</t>
+          <t>R$ 5.1437</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R$ 5.1581</t>
+          <t>R$ 5.1443</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 5.1050</t>
+          <t>R$ 5.1022</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>R$ 5.1283</t>
+          <t>R$ 5.1436</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1251,27 +1251,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R$ 5.0825</t>
+          <t>R$ 5.1437</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>R$ 5.1268</t>
+          <t>R$ 5.1443</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 5.0757</t>
+          <t>R$ 5.1022</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R$ 5.0819</t>
+          <t>R$ 5.1436</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1283,27 +1283,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R$ 5.0969</t>
+          <t>R$ 5.1437</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>R$ 5.0983</t>
+          <t>R$ 5.1443</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 5.0580</t>
+          <t>R$ 5.1022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>R$ 5.0967</t>
+          <t>R$ 5.1436</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1315,27 +1315,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R$ 5.0625</t>
+          <t>R$ 5.1029</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>R$ 5.1306</t>
+          <t>R$ 5.1513</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 5.0507</t>
+          <t>R$ 5.0746</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>R$ 5.0684</t>
+          <t>R$ 5.1030</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1347,27 +1347,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R$ 5.0875</t>
+          <t>R$ 5.1029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R$ 5.0934</t>
+          <t>R$ 5.1513</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 5.0586</t>
+          <t>R$ 5.0746</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>R$ 5.0816</t>
+          <t>R$ 5.1030</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1379,27 +1379,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R$ 5.1044</t>
+          <t>R$ 5.1029</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R$ 5.1052</t>
+          <t>R$ 5.1513</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 5.0717</t>
+          <t>R$ 5.0746</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>R$ 5.1051</t>
+          <t>R$ 5.1030</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1411,27 +1411,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R$ 5.1270</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R$ 5.1271</t>
+          <t>R$ 5.1185</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 5.0776</t>
+          <t>R$ 5.0558</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>R$ 5.1271</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1443,27 +1443,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R$ 5.1136</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R$ 5.1669</t>
+          <t>R$ 5.1185</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 5.0907</t>
+          <t>R$ 5.0558</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>R$ 5.1137</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1475,27 +1475,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R$ 5.0909</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R$ 5.1305</t>
+          <t>R$ 5.1185</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 5.0699</t>
+          <t>R$ 5.0558</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>R$ 5.0908</t>
+          <t>R$ 5.0727</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1507,27 +1507,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R$ 5.0879</t>
+          <t>R$ 5.0781</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R$ 5.0943</t>
+          <t>R$ 5.1272</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 5.0651</t>
+          <t>R$ 5.0533</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>R$ 5.0877</t>
+          <t>R$ 5.0771</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1539,27 +1539,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R$ 5.1479</t>
+          <t>R$ 5.0781</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R$ 5.1491</t>
+          <t>R$ 5.1272</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 5.0764</t>
+          <t>R$ 5.0533</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>R$ 5.1484</t>
+          <t>R$ 5.0771</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1571,27 +1571,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R$ 5.1314</t>
+          <t>R$ 5.0781</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R$ 5.1399</t>
+          <t>R$ 5.1272</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.0533</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.0771</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1603,27 +1603,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.1285</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.0702</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.1275</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1635,27 +1635,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R$ 5.1075</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R$ 5.1269</t>
+          <t>R$ 5.1285</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 5.0982</t>
+          <t>R$ 5.0702</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>R$ 5.1186</t>
+          <t>R$ 5.1275</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1667,27 +1667,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R$ 5.1635</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>R$ 5.1923</t>
+          <t>R$ 5.1285</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 5.1207</t>
+          <t>R$ 5.0702</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>R$ 5.1632</t>
+          <t>R$ 5.1275</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1699,27 +1699,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R$ 5.1709</t>
+          <t>R$ 5.1371</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>R$ 5.1814</t>
+          <t>R$ 5.1699</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 5.1361</t>
+          <t>R$ 5.1033</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>R$ 5.1708</t>
+          <t>R$ 5.1313</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1731,27 +1731,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R$ 5.1436</t>
+          <t>R$ 5.1371</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>R$ 5.1817</t>
+          <t>R$ 5.1699</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 5.1190</t>
+          <t>R$ 5.1033</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>R$ 5.1434</t>
+          <t>R$ 5.1313</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1763,27 +1763,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R$ 5.1844</t>
+          <t>R$ 5.1371</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>R$ 5.1969</t>
+          <t>R$ 5.1699</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 5.1463</t>
+          <t>R$ 5.1033</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>R$ 5.1848</t>
+          <t>R$ 5.1313</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1795,27 +1795,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R$ 5.2222</t>
+          <t>R$ 5.1230</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>R$ 5.2230</t>
+          <t>R$ 5.1581</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 5.1682</t>
+          <t>R$ 5.1050</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>R$ 5.2222</t>
+          <t>R$ 5.1283</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1827,27 +1827,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R$ 5.2206</t>
+          <t>R$ 5.1230</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R$ 5.2217</t>
+          <t>R$ 5.1581</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 5.1692</t>
+          <t>R$ 5.1050</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>R$ 5.2211</t>
+          <t>R$ 5.1283</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1859,27 +1859,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R$ 5.1747</t>
+          <t>R$ 5.1230</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R$ 5.2460</t>
+          <t>R$ 5.1581</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 5.1525</t>
+          <t>R$ 5.1050</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>R$ 5.1756</t>
+          <t>R$ 5.1283</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1891,27 +1891,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R$ 5.1818</t>
+          <t>R$ 5.0825</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>R$ 5.2279</t>
+          <t>R$ 5.1268</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 5.1652</t>
+          <t>R$ 5.0757</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>R$ 5.1872</t>
+          <t>R$ 5.0819</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1923,27 +1923,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R$ 5.1707</t>
+          <t>R$ 5.0825</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>R$ 5.2189</t>
+          <t>R$ 5.1268</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 5.1477</t>
+          <t>R$ 5.0757</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>R$ 5.1641</t>
+          <t>R$ 5.0819</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1955,27 +1955,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R$ 5.1941</t>
+          <t>R$ 5.0825</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>R$ 5.2171</t>
+          <t>R$ 5.1268</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 5.1616</t>
+          <t>R$ 5.0757</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>R$ 5.1940</t>
+          <t>R$ 5.0819</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1987,27 +1987,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R$ 5.2075</t>
+          <t>R$ 5.0969</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R$ 5.2315</t>
+          <t>R$ 5.0983</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 5.1834</t>
+          <t>R$ 5.0580</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>R$ 5.2076</t>
+          <t>R$ 5.0967</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2019,27 +2019,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R$ 5.1977</t>
+          <t>R$ 5.0969</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>R$ 5.2356</t>
+          <t>R$ 5.0983</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 5.1754</t>
+          <t>R$ 5.0580</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>R$ 5.1985</t>
+          <t>R$ 5.0967</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2051,27 +2051,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R$ 5.1565</t>
+          <t>R$ 5.0969</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R$ 5.2207</t>
+          <t>R$ 5.0983</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 5.1354</t>
+          <t>R$ 5.0580</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>R$ 5.1562</t>
+          <t>R$ 5.0967</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2083,27 +2083,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R$ 5.1514</t>
+          <t>R$ 5.0625</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R$ 5.1701</t>
+          <t>R$ 5.1306</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 5.1246</t>
+          <t>R$ 5.0507</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>R$ 5.1510</t>
+          <t>R$ 5.0684</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2115,27 +2115,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R$ 5.1815</t>
+          <t>R$ 5.0625</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R$ 5.1823</t>
+          <t>R$ 5.1306</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 5.1318</t>
+          <t>R$ 5.0507</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>R$ 5.1820</t>
+          <t>R$ 5.0684</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2147,27 +2147,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R$ 5.1221</t>
+          <t>R$ 5.0625</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R$ 5.1901</t>
+          <t>R$ 5.1306</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 5.0990</t>
+          <t>R$ 5.0507</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>R$ 5.1222</t>
+          <t>R$ 5.0684</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2179,27 +2179,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R$ 5.1019</t>
+          <t>R$ 5.0875</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R$ 5.1078</t>
+          <t>R$ 5.0934</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 5.0579</t>
+          <t>R$ 5.0586</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>R$ 5.0993</t>
+          <t>R$ 5.0816</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2211,27 +2211,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R$ 5.0751</t>
+          <t>R$ 5.0875</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R$ 5.1345</t>
+          <t>R$ 5.0934</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 5.0503</t>
+          <t>R$ 5.0586</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>R$ 5.0747</t>
+          <t>R$ 5.0816</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2243,27 +2243,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R$ 5.0609</t>
+          <t>R$ 5.0875</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>R$ 5.0724</t>
+          <t>R$ 5.0934</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 5.0402</t>
+          <t>R$ 5.0586</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>R$ 5.0611</t>
+          <t>R$ 5.0816</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2275,27 +2275,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R$ 5.1138</t>
+          <t>R$ 5.1044</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R$ 5.1302</t>
+          <t>R$ 5.1052</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 5.0690</t>
+          <t>R$ 5.0717</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>R$ 5.1133</t>
+          <t>R$ 5.1051</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2307,27 +2307,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R$ 5.1921</t>
+          <t>R$ 5.1044</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>R$ 5.1944</t>
+          <t>R$ 5.1052</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 5.1358</t>
+          <t>R$ 5.0717</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>R$ 5.1924</t>
+          <t>R$ 5.1051</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2339,27 +2339,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R$ 5.1901</t>
+          <t>R$ 5.1044</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R$ 5.2093</t>
+          <t>R$ 5.1052</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 5.1532</t>
+          <t>R$ 5.0717</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>R$ 5.1904</t>
+          <t>R$ 5.1051</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2371,27 +2371,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R$ 5.2031</t>
+          <t>R$ 5.1270</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>R$ 5.2038</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 5.1510</t>
+          <t>R$ 5.0776</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>R$ 5.2027</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2403,27 +2403,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R$ 5.1770</t>
+          <t>R$ 5.1270</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>R$ 5.2255</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 5.1324</t>
+          <t>R$ 5.0776</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>R$ 5.1797</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2435,27 +2435,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R$ 5.0607</t>
+          <t>R$ 5.1270</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R$ 5.1792</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 5.0499</t>
+          <t>R$ 5.0776</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>R$ 5.0633</t>
+          <t>R$ 5.1271</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2467,27 +2467,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R$ 5.0774</t>
+          <t>R$ 5.1136</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R$ 5.0804</t>
+          <t>R$ 5.1669</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 5.0562</t>
+          <t>R$ 5.0907</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>R$ 5.0716</t>
+          <t>R$ 5.1137</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2499,27 +2499,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R$ 5.0207</t>
+          <t>R$ 5.1136</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R$ 5.0678</t>
+          <t>R$ 5.1669</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 4.9978</t>
+          <t>R$ 5.0907</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>R$ 5.0205</t>
+          <t>R$ 5.1137</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2531,27 +2531,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R$ 5.0386</t>
+          <t>R$ 5.1136</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R$ 5.0394</t>
+          <t>R$ 5.1669</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 5.0024</t>
+          <t>R$ 5.0907</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>R$ 5.0328</t>
+          <t>R$ 5.1137</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2563,27 +2563,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R$ 5.0392</t>
+          <t>R$ 5.0909</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R$ 5.0570</t>
+          <t>R$ 5.1305</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 5.0156</t>
+          <t>R$ 5.0699</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>R$ 5.0388</t>
+          <t>R$ 5.0908</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2595,27 +2595,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R$ 5.0517</t>
+          <t>R$ 5.0909</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R$ 5.1049</t>
+          <t>R$ 5.1305</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 5.0352</t>
+          <t>R$ 5.0699</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>R$ 5.0517</t>
+          <t>R$ 5.0908</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2627,27 +2627,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R$ 5.0729</t>
+          <t>R$ 5.0909</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R$ 5.0834</t>
+          <t>R$ 5.1305</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 5.0398</t>
+          <t>R$ 5.0699</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>R$ 5.0729</t>
+          <t>R$ 5.0908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2659,27 +2659,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R$ 5.0445</t>
+          <t>R$ 5.0879</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R$ 5.1045</t>
+          <t>R$ 5.0943</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 5.0232</t>
+          <t>R$ 5.0651</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>R$ 5.0443</t>
+          <t>R$ 5.0877</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2691,27 +2691,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R$ 5.0104</t>
+          <t>R$ 5.0879</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R$ 5.0720</t>
+          <t>R$ 5.0943</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 5.0026</t>
+          <t>R$ 5.0651</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>R$ 5.0104</t>
+          <t>R$ 5.0877</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2723,27 +2723,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R$ 5.0257</t>
+          <t>R$ 5.0879</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R$ 5.0363</t>
+          <t>R$ 5.0943</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 4.9913</t>
+          <t>R$ 5.0651</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>R$ 5.0251</t>
+          <t>R$ 5.0877</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2755,27 +2755,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R$ 5.0171</t>
+          <t>R$ 5.1479</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R$ 5.0509</t>
+          <t>R$ 5.1491</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 4.9961</t>
+          <t>R$ 5.0764</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>R$ 5.0174</t>
+          <t>R$ 5.1484</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2787,27 +2787,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R$ 5.0117</t>
+          <t>R$ 5.1479</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R$ 5.0389</t>
+          <t>R$ 5.1491</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 4.9938</t>
+          <t>R$ 5.0764</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>R$ 5.0118</t>
+          <t>R$ 5.1484</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2819,27 +2819,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>R$ 5.0582</t>
+          <t>R$ 5.1479</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>R$ 5.0878</t>
+          <t>R$ 5.1491</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 5.0021</t>
+          <t>R$ 5.0764</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>R$ 5.0583</t>
+          <t>R$ 5.1484</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2851,27 +2851,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>R$ 5.0056</t>
+          <t>R$ 5.1314</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>R$ 5.0737</t>
+          <t>R$ 5.1399</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 4.9842</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>R$ 5.0088</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2883,27 +2883,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>R$ 5.0604</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R$ 5.0668</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 5.0077</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>R$ 5.0606</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2915,27 +2915,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>R$ 5.0041</t>
+          <t>R$ 5.1075</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>R$ 5.1022</t>
+          <t>R$ 5.1269</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 4.9780</t>
+          <t>R$ 5.0982</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>R$ 4.9987</t>
+          <t>R$ 5.1186</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2947,27 +2947,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>R$ 5.0249</t>
+          <t>R$ 5.1635</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>R$ 5.0257</t>
+          <t>R$ 5.1923</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 4.9718</t>
+          <t>R$ 5.1207</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>R$ 5.0198</t>
+          <t>R$ 5.1632</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2979,27 +2979,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>R$ 4.9097</t>
+          <t>R$ 5.1709</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R$ 4.9529</t>
+          <t>R$ 5.1814</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 4.8864</t>
+          <t>R$ 5.1361</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>R$ 4.9105</t>
+          <t>R$ 5.1708</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3011,27 +3011,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>R$ 4.9064</t>
+          <t>R$ 5.1436</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>R$ 4.9400</t>
+          <t>R$ 5.1817</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 4.8812</t>
+          <t>R$ 5.1190</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>R$ 4.9064</t>
+          <t>R$ 5.1434</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3043,27 +3043,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>R$ 4.9133</t>
+          <t>R$ 5.1844</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>R$ 4.9371</t>
+          <t>R$ 5.1969</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 4.8831</t>
+          <t>R$ 5.1463</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>R$ 4.9132</t>
+          <t>R$ 5.1848</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3075,27 +3075,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>R$ 4.9449</t>
+          <t>R$ 5.2222</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>R$ 4.9452</t>
+          <t>R$ 5.2230</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 4.8912</t>
+          <t>R$ 5.1682</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>R$ 4.9388</t>
+          <t>R$ 5.2222</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3107,27 +3107,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>R$ 4.9323</t>
+          <t>R$ 5.2206</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>R$ 4.9585</t>
+          <t>R$ 5.2217</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 4.9052</t>
+          <t>R$ 5.1692</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>R$ 4.9377</t>
+          <t>R$ 5.2211</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3139,27 +3139,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>R$ 4.9273</t>
+          <t>R$ 5.1747</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>R$ 4.9557</t>
+          <t>R$ 5.2460</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 4.8922</t>
+          <t>R$ 5.1525</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>R$ 4.9273</t>
+          <t>R$ 5.1756</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3171,27 +3171,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>R$ 4.9848</t>
+          <t>R$ 5.1818</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>R$ 4.9850</t>
+          <t>R$ 5.2279</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 4.9177</t>
+          <t>R$ 5.1652</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>R$ 4.9841</t>
+          <t>R$ 5.1872</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3203,27 +3203,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>R$ 4.9519</t>
+          <t>R$ 5.1707</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>R$ 4.9858</t>
+          <t>R$ 5.2189</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 4.9445</t>
+          <t>R$ 5.1477</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>R$ 4.9565</t>
+          <t>R$ 5.1641</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3235,27 +3235,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>R$ 4.9695</t>
+          <t>R$ 5.1941</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>R$ 4.9736</t>
+          <t>R$ 5.2171</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 4.9485</t>
+          <t>R$ 5.1616</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>R$ 4.9697</t>
+          <t>R$ 5.1940</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3267,27 +3267,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>R$ 5.0175</t>
+          <t>R$ 5.2075</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>R$ 5.0184</t>
+          <t>R$ 5.2315</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 4.9716</t>
+          <t>R$ 5.1834</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>R$ 5.0172</t>
+          <t>R$ 5.2076</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3299,27 +3299,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>R$ 4.9943</t>
+          <t>R$ 5.1977</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>R$ 5.0392</t>
+          <t>R$ 5.2356</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 4.9676</t>
+          <t>R$ 5.1754</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>R$ 4.9947</t>
+          <t>R$ 5.1985</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3331,27 +3331,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>R$ 4.9996</t>
+          <t>R$ 5.1565</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>R$ 5.0481</t>
+          <t>R$ 5.2207</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 4.9754</t>
+          <t>R$ 5.1354</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>R$ 5.0005</t>
+          <t>R$ 5.1562</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3363,27 +3363,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>R$ 4.9791</t>
+          <t>R$ 5.1514</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R$ 5.0205</t>
+          <t>R$ 5.1701</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 4.9638</t>
+          <t>R$ 5.1246</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>R$ 4.9794</t>
+          <t>R$ 5.1510</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3395,27 +3395,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>R$ 5.0308</t>
+          <t>R$ 5.1815</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>R$ 5.0640</t>
+          <t>R$ 5.1823</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 4.9946</t>
+          <t>R$ 5.1318</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>R$ 5.0318</t>
+          <t>R$ 5.1820</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3427,27 +3427,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>R$ 4.9849</t>
+          <t>R$ 5.1221</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R$ 4.9870</t>
+          <t>R$ 5.1901</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 4.9439</t>
+          <t>R$ 5.0990</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>R$ 4.9818</t>
+          <t>R$ 5.1222</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3459,27 +3459,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>R$ 5.0080</t>
+          <t>R$ 5.1019</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>R$ 5.0160</t>
+          <t>R$ 5.1078</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 4.9569</t>
+          <t>R$ 5.0579</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>R$ 5.0093</t>
+          <t>R$ 5.0993</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3491,27 +3491,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>R$ 4.9524</t>
+          <t>R$ 5.0751</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>R$ 4.9764</t>
+          <t>R$ 5.1345</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 4.9464</t>
+          <t>R$ 5.0503</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>R$ 4.9526</t>
+          <t>R$ 5.0747</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3523,27 +3523,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>R$ 5.0063</t>
+          <t>R$ 5.0609</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R$ 5.0460</t>
+          <t>R$ 5.0724</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 4.9688</t>
+          <t>R$ 5.0402</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>R$ 5.0040</t>
+          <t>R$ 5.0611</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3555,27 +3555,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>R$ 4.9871</t>
+          <t>R$ 5.1138</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R$ 4.9938</t>
+          <t>R$ 5.1302</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 4.9471</t>
+          <t>R$ 5.0690</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>R$ 4.9907</t>
+          <t>R$ 5.1133</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3587,27 +3587,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>R$ 4.9924</t>
+          <t>R$ 5.1921</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R$ 5.0131</t>
+          <t>R$ 5.1944</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 4.9777</t>
+          <t>R$ 5.1358</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>R$ 4.9931</t>
+          <t>R$ 5.1924</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3619,27 +3619,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>R$ 4.9848</t>
+          <t>R$ 5.1901</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R$ 5.0001</t>
+          <t>R$ 5.2093</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 4.9746</t>
+          <t>R$ 5.1532</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>R$ 4.9857</t>
+          <t>R$ 5.1904</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3651,27 +3651,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>R$ 4.9944</t>
+          <t>R$ 5.2031</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>R$ 4.9965</t>
+          <t>R$ 5.2038</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 4.9660</t>
+          <t>R$ 5.1510</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>R$ 4.9953</t>
+          <t>R$ 5.2027</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3683,27 +3683,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>R$ 5.0050</t>
+          <t>R$ 5.1770</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>R$ 5.0445</t>
+          <t>R$ 5.2255</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 4.9942</t>
+          <t>R$ 5.1324</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>R$ 5.0052</t>
+          <t>R$ 5.1797</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3715,27 +3715,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>R$ 5.0958</t>
+          <t>R$ 5.0607</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>R$ 5.1103</t>
+          <t>R$ 5.1792</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 5.0058</t>
+          <t>R$ 5.0499</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>R$ 5.0962</t>
+          <t>R$ 5.0633</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3747,27 +3747,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>R$ 5.1002</t>
+          <t>R$ 5.0774</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>R$ 5.1404</t>
+          <t>R$ 5.0804</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 5.0649</t>
+          <t>R$ 5.0562</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>R$ 5.0992</t>
+          <t>R$ 5.0716</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3779,27 +3779,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>R$ 5.1506</t>
+          <t>R$ 5.0207</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>R$ 5.1747</t>
+          <t>R$ 5.0678</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 5.0652</t>
+          <t>R$ 4.9978</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>R$ 5.1500</t>
+          <t>R$ 5.0205</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3811,27 +3811,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>R$ 5.1383</t>
+          <t>R$ 5.0386</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>R$ 5.1701</t>
+          <t>R$ 5.0394</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 5.1281</t>
+          <t>R$ 5.0024</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>R$ 5.1392</t>
+          <t>R$ 5.0328</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3843,27 +3843,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>R$ 5.1579</t>
+          <t>R$ 5.0392</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>R$ 5.1755</t>
+          <t>R$ 5.0570</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 5.1372</t>
+          <t>R$ 5.0156</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>R$ 5.1555</t>
+          <t>R$ 5.0388</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3875,27 +3875,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>R$ 5.1564</t>
+          <t>R$ 5.0517</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>R$ 5.1578</t>
+          <t>R$ 5.1049</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 5.1493</t>
+          <t>R$ 5.0352</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>R$ 5.1572</t>
+          <t>R$ 5.0517</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3907,27 +3907,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>R$ 5.1545</t>
+          <t>R$ 5.0729</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>R$ 5.1870</t>
+          <t>R$ 5.0834</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 5.1430</t>
+          <t>R$ 5.0398</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>R$ 5.1546</t>
+          <t>R$ 5.0729</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3939,27 +3939,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>R$ 5.1928</t>
+          <t>R$ 5.0445</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>R$ 5.2021</t>
+          <t>R$ 5.1045</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 5.1482</t>
+          <t>R$ 5.0232</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>R$ 5.1921</t>
+          <t>R$ 5.0443</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3971,27 +3971,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>R$ 5.2640</t>
+          <t>R$ 5.0104</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>R$ 5.2648</t>
+          <t>R$ 5.0720</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 5.2024</t>
+          <t>R$ 5.0026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>R$ 5.2637</t>
+          <t>R$ 5.0104</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4003,27 +4003,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>R$ 5.2380</t>
+          <t>R$ 5.0257</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>R$ 5.2703</t>
+          <t>R$ 5.0363</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 5.2190</t>
+          <t>R$ 4.9913</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>R$ 5.2379</t>
+          <t>R$ 5.0251</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4035,27 +4035,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>R$ 5.2351</t>
+          <t>R$ 5.0171</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>R$ 5.2752</t>
+          <t>R$ 5.0509</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 5.2114</t>
+          <t>R$ 4.9961</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>R$ 5.2312</t>
+          <t>R$ 5.0174</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4067,27 +4067,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>R$ 5.2368</t>
+          <t>R$ 5.0117</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>R$ 5.2568</t>
+          <t>R$ 5.0389</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 5.2163</t>
+          <t>R$ 4.9938</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>R$ 5.2364</t>
+          <t>R$ 5.0118</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4099,27 +4099,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>R$ 5.2326</t>
+          <t>R$ 5.0582</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>R$ 5.2575</t>
+          <t>R$ 5.0878</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 5.2087</t>
+          <t>R$ 5.0021</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>R$ 5.2321</t>
+          <t>R$ 5.0583</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4131,27 +4131,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>R$ 5.2329</t>
+          <t>R$ 5.0056</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>R$ 5.2883</t>
+          <t>R$ 5.0737</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 5.2220</t>
+          <t>R$ 4.9842</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>R$ 5.2343</t>
+          <t>R$ 5.0088</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4163,27 +4163,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>R$ 5.3119</t>
+          <t>R$ 5.0604</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>R$ 5.3659</t>
+          <t>R$ 5.0668</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 5.2493</t>
+          <t>R$ 5.0077</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>R$ 5.3087</t>
+          <t>R$ 5.0606</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4195,27 +4195,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>R$ 5.2199</t>
+          <t>R$ 5.0041</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>R$ 5.3067</t>
+          <t>R$ 5.1022</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 5.2126</t>
+          <t>R$ 4.9780</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>R$ 5.2203</t>
+          <t>R$ 4.9987</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4227,27 +4227,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>R$ 5.2621</t>
+          <t>R$ 5.0249</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R$ 5.3237</t>
+          <t>R$ 5.0257</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 5.2308</t>
+          <t>R$ 4.9718</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>R$ 5.2617</t>
+          <t>R$ 5.0198</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4259,27 +4259,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>R$ 5.1929</t>
+          <t>R$ 4.9097</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>R$ 5.2279</t>
+          <t>R$ 4.9529</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 5.1765</t>
+          <t>R$ 4.8864</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>R$ 5.1929</t>
+          <t>R$ 4.9105</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4291,27 +4291,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>R$ 5.2334</t>
+          <t>R$ 4.9064</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>R$ 5.2485</t>
+          <t>R$ 4.9400</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 5.1862</t>
+          <t>R$ 4.8812</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>R$ 5.2318</t>
+          <t>R$ 4.9064</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4323,27 +4323,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>R$ 5.3291</t>
+          <t>R$ 4.9133</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>R$ 5.3843</t>
+          <t>R$ 4.9371</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 5.2474</t>
+          <t>R$ 4.8831</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>R$ 5.3226</t>
+          <t>R$ 4.9132</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4355,27 +4355,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>R$ 5.2439</t>
+          <t>R$ 4.9449</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>R$ 5.2854</t>
+          <t>R$ 4.9452</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 5.2140</t>
+          <t>R$ 4.8912</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>R$ 5.2451</t>
+          <t>R$ 4.9388</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4387,27 +4387,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>R$ 5.1514</t>
+          <t>R$ 4.9323</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>R$ 5.2330</t>
+          <t>R$ 4.9585</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 5.1550</t>
+          <t>R$ 4.9052</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>R$ 5.1685</t>
+          <t>R$ 4.9377</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4419,27 +4419,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>R$ 5.1624</t>
+          <t>R$ 4.9273</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>R$ 5.2131</t>
+          <t>R$ 4.9557</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 5.1499</t>
+          <t>R$ 4.8922</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>R$ 5.1639</t>
+          <t>R$ 4.9273</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4451,27 +4451,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>R$ 5.2053</t>
+          <t>R$ 4.9848</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>R$ 5.2318</t>
+          <t>R$ 4.9850</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 5.1378</t>
+          <t>R$ 4.9177</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>R$ 5.2035</t>
+          <t>R$ 4.9841</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4483,27 +4483,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>R$ 5.2435</t>
+          <t>R$ 4.9519</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R$ 5.2941</t>
+          <t>R$ 4.9858</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 5.2128</t>
+          <t>R$ 4.9445</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>R$ 5.2399</t>
+          <t>R$ 4.9565</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4515,27 +4515,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>R$ 5.2634</t>
+          <t>R$ 4.9695</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>R$ 5.3133</t>
+          <t>R$ 4.9736</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 5.2565</t>
+          <t>R$ 4.9485</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>R$ 5.2623</t>
+          <t>R$ 4.9697</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4547,27 +4547,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>R$ 5.2301</t>
+          <t>R$ 5.0175</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>R$ 5.2828</t>
+          <t>R$ 5.0184</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 5.2204</t>
+          <t>R$ 4.9716</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>R$ 5.2301</t>
+          <t>R$ 5.0172</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4579,27 +4579,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>R$ 5.2773</t>
+          <t>R$ 4.9943</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>R$ 5.2811</t>
+          <t>R$ 5.0392</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 5.1895</t>
+          <t>R$ 4.9676</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>R$ 5.2758</t>
+          <t>R$ 4.9947</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4611,27 +4611,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>R$ 5.1703</t>
+          <t>R$ 4.9996</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>R$ 5.3385</t>
+          <t>R$ 5.0481</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 5.1636</t>
+          <t>R$ 4.9754</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>R$ 5.1703</t>
+          <t>R$ 5.0005</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4643,27 +4643,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>R$ 5.1296</t>
+          <t>R$ 4.9791</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>R$ 5.2392</t>
+          <t>R$ 5.0205</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 5.1220</t>
+          <t>R$ 4.9638</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>R$ 5.1290</t>
+          <t>R$ 4.9794</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4675,27 +4675,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>R$ 5.1366</t>
+          <t>R$ 5.0308</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>R$ 5.1665</t>
+          <t>R$ 5.0640</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 5.1224</t>
+          <t>R$ 4.9946</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>R$ 5.1366</t>
+          <t>R$ 5.0318</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4707,27 +4707,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>R$ 5.1242</t>
+          <t>R$ 4.9849</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>R$ 5.1548</t>
+          <t>R$ 4.9870</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 5.1176</t>
+          <t>R$ 4.9439</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>R$ 5.1243</t>
+          <t>R$ 4.9818</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4739,27 +4739,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>R$ 5.1520</t>
+          <t>R$ 5.0080</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>R$ 5.1634</t>
+          <t>R$ 5.0160</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 5.1171</t>
+          <t>R$ 4.9569</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>R$ 5.1520</t>
+          <t>R$ 5.0093</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4771,27 +4771,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>R$ 5.1709</t>
+          <t>R$ 4.9524</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>R$ 5.1826</t>
+          <t>R$ 4.9764</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 5.1367</t>
+          <t>R$ 4.9464</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>R$ 5.1708</t>
+          <t>R$ 4.9526</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4803,27 +4803,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>R$ 5.1765</t>
+          <t>R$ 5.0063</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>R$ 5.1931</t>
+          <t>R$ 5.0460</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 5.1371</t>
+          <t>R$ 4.9688</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>R$ 5.1781</t>
+          <t>R$ 5.0040</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4835,27 +4835,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>R$ 5.2088</t>
+          <t>R$ 4.9871</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>R$ 5.2212</t>
+          <t>R$ 4.9938</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 5.1738</t>
+          <t>R$ 4.9471</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>R$ 5.2088</t>
+          <t>R$ 4.9907</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4867,27 +4867,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>R$ 5.2344</t>
+          <t>R$ 4.9924</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>R$ 5.2494</t>
+          <t>R$ 5.0131</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 5.2084</t>
+          <t>R$ 4.9777</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>R$ 5.2345</t>
+          <t>R$ 4.9931</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4899,27 +4899,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>R$ 5.2205</t>
+          <t>R$ 4.9848</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>R$ 5.2235</t>
+          <t>R$ 5.0001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 5.1928</t>
+          <t>R$ 4.9746</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>R$ 5.2224</t>
+          <t>R$ 4.9857</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4931,27 +4931,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>R$ 5.2439</t>
+          <t>R$ 4.9944</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>R$ 5.2540</t>
+          <t>R$ 4.9965</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 5.2131</t>
+          <t>R$ 4.9660</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>R$ 5.2439</t>
+          <t>R$ 4.9953</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4963,27 +4963,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>R$ 5.2179</t>
+          <t>R$ 5.0050</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>R$ 5.2395</t>
+          <t>R$ 5.0445</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 5.2166</t>
+          <t>R$ 4.9942</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>R$ 5.2207</t>
+          <t>R$ 5.0052</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4995,27 +4995,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>R$ 5.2139</t>
+          <t>R$ 5.0958</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>R$ 5.2416</t>
+          <t>R$ 5.1103</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 5.2041</t>
+          <t>R$ 5.0058</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>R$ 5.2115</t>
+          <t>R$ 5.0962</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5027,27 +5027,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>R$ 5.1987</t>
+          <t>R$ 5.1002</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>R$ 5.2000</t>
+          <t>R$ 5.1404</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 5.1523</t>
+          <t>R$ 5.0649</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>R$ 5.1993</t>
+          <t>R$ 5.0992</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5059,27 +5059,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>R$ 5.1962</t>
+          <t>R$ 5.1506</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>R$ 5.2080</t>
+          <t>R$ 5.1747</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 5.1721</t>
+          <t>R$ 5.0652</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>R$ 5.1950</t>
+          <t>R$ 5.1500</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5091,27 +5091,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>R$ 5.1916</t>
+          <t>R$ 5.1383</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>R$ 5.2384</t>
+          <t>R$ 5.1701</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 5.1786</t>
+          <t>R$ 5.1281</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>R$ 5.1912</t>
+          <t>R$ 5.1392</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5123,27 +5123,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>R$ 5.2159</t>
+          <t>R$ 5.1579</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>R$ 5.2381</t>
+          <t>R$ 5.1755</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 5.1727</t>
+          <t>R$ 5.1372</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>R$ 5.2172</t>
+          <t>R$ 5.1555</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5155,27 +5155,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>R$ 5.2705</t>
+          <t>R$ 5.1564</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>R$ 5.3397</t>
+          <t>R$ 5.1578</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 5.2659</t>
+          <t>R$ 5.1493</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>R$ 5.2707</t>
+          <t>R$ 5.1572</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5187,27 +5187,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>R$ 5.2380</t>
+          <t>R$ 5.1545</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>R$ 5.2786</t>
+          <t>R$ 5.1870</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 5.2308</t>
+          <t>R$ 5.1430</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>R$ 5.2384</t>
+          <t>R$ 5.1546</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5219,27 +5219,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>R$ 5.2375</t>
+          <t>R$ 5.1928</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>R$ 5.2567</t>
+          <t>R$ 5.2021</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>R$ 5.2113</t>
+          <t>R$ 5.1482</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>R$ 5.2370</t>
+          <t>R$ 5.1921</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5251,27 +5251,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>R$ 5.2594</t>
+          <t>R$ 5.2640</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>R$ 5.2758</t>
+          <t>R$ 5.2648</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 5.2018</t>
+          <t>R$ 5.2024</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>R$ 5.2604</t>
+          <t>R$ 5.2637</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5283,27 +5283,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>R$ 5.2550</t>
+          <t>R$ 5.2380</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>R$ 5.3108</t>
+          <t>R$ 5.2703</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 5.2350</t>
+          <t>R$ 5.2190</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>R$ 5.2594</t>
+          <t>R$ 5.2379</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5315,27 +5315,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>R$ 5.1892</t>
+          <t>R$ 5.2351</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>R$ 5.2475</t>
+          <t>R$ 5.2752</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>R$ 5.1787</t>
+          <t>R$ 5.2114</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>R$ 5.1915</t>
+          <t>R$ 5.2312</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5347,27 +5347,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>R$ 5.1971</t>
+          <t>R$ 5.2368</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>R$ 5.2459</t>
+          <t>R$ 5.2568</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 5.1690</t>
+          <t>R$ 5.2163</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>R$ 5.1954</t>
+          <t>R$ 5.2364</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5379,27 +5379,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>R$ 5.1836</t>
+          <t>R$ 5.2326</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>R$ 5.2184</t>
+          <t>R$ 5.2575</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 5.1699</t>
+          <t>R$ 5.2087</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>R$ 5.1835</t>
+          <t>R$ 5.2321</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5411,27 +5411,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>R$ 5.2791</t>
+          <t>R$ 5.2329</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>R$ 5.3086</t>
+          <t>R$ 5.2883</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 5.2042</t>
+          <t>R$ 5.2220</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>R$ 5.2726</t>
+          <t>R$ 5.2343</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5443,27 +5443,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>R$ 5.2889</t>
+          <t>R$ 5.3119</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>R$ 5.3541</t>
+          <t>R$ 5.3659</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 5.2533</t>
+          <t>R$ 5.2493</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>R$ 5.2858</t>
+          <t>R$ 5.3087</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5475,27 +5475,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>R$ 5.2837</t>
+          <t>R$ 5.2199</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>R$ 5.3023</t>
+          <t>R$ 5.3067</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 5.2762</t>
+          <t>R$ 5.2126</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>R$ 5.2834</t>
+          <t>R$ 5.2203</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5507,27 +5507,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>R$ 5.3188</t>
+          <t>R$ 5.2621</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>R$ 5.3462</t>
+          <t>R$ 5.3237</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 5.2848</t>
+          <t>R$ 5.2308</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>R$ 5.3181</t>
+          <t>R$ 5.2617</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5539,27 +5539,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>R$ 5.3743</t>
+          <t>R$ 5.1929</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>R$ 5.3761</t>
+          <t>R$ 5.2279</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 5.3131</t>
+          <t>R$ 5.1765</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>R$ 5.3736</t>
+          <t>R$ 5.1929</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5571,27 +5571,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>R$ 5.3687</t>
+          <t>R$ 5.2334</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>R$ 5.4187</t>
+          <t>R$ 5.2485</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 5.3530</t>
+          <t>R$ 5.1862</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>R$ 5.3687</t>
+          <t>R$ 5.2318</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5603,27 +5603,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>R$ 5.3677</t>
+          <t>R$ 5.3291</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>R$ 5.3793</t>
+          <t>R$ 5.3843</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>R$ 5.3447</t>
+          <t>R$ 5.2474</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>R$ 5.3609</t>
+          <t>R$ 5.3226</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5635,27 +5635,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>R$ 5.3679</t>
+          <t>R$ 5.2439</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>R$ 5.3918</t>
+          <t>R$ 5.2854</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 5.3596</t>
+          <t>R$ 5.2140</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>R$ 5.3661</t>
+          <t>R$ 5.2451</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5667,27 +5667,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>R$ 5.3961</t>
+          <t>R$ 5.1514</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>R$ 5.4018</t>
+          <t>R$ 5.2330</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 5.3563</t>
+          <t>R$ 5.1550</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>R$ 5.3957</t>
+          <t>R$ 5.1685</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5699,27 +5699,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>R$ 5.3713</t>
+          <t>R$ 5.1624</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>R$ 5.4127</t>
+          <t>R$ 5.2131</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 5.3571</t>
+          <t>R$ 5.1499</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>R$ 5.3712</t>
+          <t>R$ 5.1639</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -5731,27 +5731,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>R$ 5.3737</t>
+          <t>R$ 5.2053</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>R$ 5.3907</t>
+          <t>R$ 5.2318</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 5.3595</t>
+          <t>R$ 5.1378</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>R$ 5.3736</t>
+          <t>R$ 5.2035</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -5763,30 +5763,1310 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>R$ 5.2435</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>R$ 5.2941</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>R$ 5.2128</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>R$ 5.2399</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>R$ 5.2634</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>R$ 5.3133</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>R$ 5.2565</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>R$ 5.2623</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>R$ 5.2301</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>R$ 5.2828</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>R$ 5.2204</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>R$ 5.2301</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>R$ 5.2773</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>R$ 5.2811</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>R$ 5.1895</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>R$ 5.2758</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>R$ 5.1703</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>R$ 5.3385</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>R$ 5.1636</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>R$ 5.1703</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>R$ 5.1296</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>R$ 5.2392</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>R$ 5.1220</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>R$ 5.1290</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>R$ 5.1366</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>R$ 5.1665</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>R$ 5.1224</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>R$ 5.1366</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>R$ 5.1242</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>R$ 5.1548</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>R$ 5.1176</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>R$ 5.1243</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>R$ 5.1520</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>R$ 5.1634</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>R$ 5.1171</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>R$ 5.1520</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>R$ 5.1709</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>R$ 5.1826</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>R$ 5.1367</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>R$ 5.1708</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>R$ 5.1765</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>R$ 5.1931</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>R$ 5.1371</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>R$ 5.1781</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>R$ 5.2088</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>R$ 5.2212</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>R$ 5.1738</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>R$ 5.2088</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>R$ 5.2344</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>R$ 5.2494</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>R$ 5.2084</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>R$ 5.2345</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>R$ 5.2205</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>R$ 5.2235</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>R$ 5.1928</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>R$ 5.2224</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>R$ 5.2439</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>R$ 5.2540</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>R$ 5.2131</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>R$ 5.2439</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>R$ 5.2179</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>R$ 5.2395</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>R$ 5.2166</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>R$ 5.2207</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>R$ 5.2139</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>R$ 5.2416</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>R$ 5.2041</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>R$ 5.2115</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>R$ 5.1987</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>R$ 5.2000</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>R$ 5.1523</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>R$ 5.1993</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>R$ 5.1962</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>R$ 5.2080</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>R$ 5.1721</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>R$ 5.1950</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>R$ 5.1916</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>R$ 5.2384</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>R$ 5.1786</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>R$ 5.1912</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>R$ 5.2159</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>R$ 5.2381</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>R$ 5.1727</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>R$ 5.2172</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>R$ 5.2705</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>R$ 5.3397</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>R$ 5.2659</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>R$ 5.2707</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>R$ 5.2380</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>R$ 5.2786</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>R$ 5.2308</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>R$ 5.2384</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>R$ 5.2375</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>R$ 5.2567</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>R$ 5.2113</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>R$ 5.2370</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>R$ 5.2594</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>R$ 5.2758</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>R$ 5.2018</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>R$ 5.2604</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>R$ 5.2550</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>R$ 5.3108</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>R$ 5.2350</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>R$ 5.2594</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>R$ 5.1892</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>R$ 5.2475</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>R$ 5.1787</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>R$ 5.1915</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>R$ 5.1971</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>R$ 5.2459</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>R$ 5.1690</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>R$ 5.1954</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>R$ 5.1836</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>R$ 5.2184</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>R$ 5.1699</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>R$ 5.1835</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>R$ 5.2791</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>R$ 5.3086</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>R$ 5.2042</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>R$ 5.2726</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>R$ 5.2889</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>R$ 5.3541</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>R$ 5.2533</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>R$ 5.2858</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>R$ 5.2837</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>R$ 5.3023</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>R$ 5.2762</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>R$ 5.2834</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>R$ 5.3188</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>R$ 5.3462</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>R$ 5.2848</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>R$ 5.3181</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>R$ 5.3743</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>R$ 5.3761</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>R$ 5.3131</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>R$ 5.3736</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>R$ 5.3687</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>R$ 5.4187</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>R$ 5.3530</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>R$ 5.3687</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>R$ 5.3677</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>R$ 5.3793</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>R$ 5.3447</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>R$ 5.3609</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>R$ 5.3679</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>R$ 5.3918</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>R$ 5.3596</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>R$ 5.3661</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>R$ 5.3961</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>R$ 5.4018</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>R$ 5.3563</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>R$ 5.3957</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>14/01/2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>R$ 5.3713</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>R$ 5.4127</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>R$ 5.3571</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>R$ 5.3712</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>R$ 5.3737</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>R$ 5.3907</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>R$ 5.3595</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>R$ 5.3736</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>R$ 5.3703</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>R$ 5.4062</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>R$ 5.3489</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>R$ 5.3650</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>0</t>
         </is>
